--- a/textbook_examples/mod01_wide_long.xlsx
+++ b/textbook_examples/mod01_wide_long.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Wide and long" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Start here" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Wide" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Long" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -41,6 +43,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="000563C1"/>
+      <sz val="11"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <color rgb="0024302A"/>
       <sz val="10"/>
     </font>
@@ -49,11 +57,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -81,29 +84,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -469,7 +473,97 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>The same data in two shapes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>The next two tabs hold exactly the same numbers — three rural municipalities, three crops, one year — laid out two different ways.  Open them side by side and compare.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1"/>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Wide</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>One row per RM.  Each crop is its own column, so the crop name is a column HEADING.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1"/>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>One row per RM and crop.  The crop is a VALUE in its own column, and every yield is stacked into one column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1"/>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Neither is wrong; they suit different jobs.  Wide is easy to read and quick for column-at-a-time arithmetic — average the Canola column and you are done.  Long is what you need to summarize BY the stacked thing: a PivotTable can only group by a field that lives in its own column, so to get average yield per crop, the crop has to be a column of values rather than a set of headings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1"/>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Try it: on the Long tab you can build that PivotTable in one move.  On the Wide tab there is no Crop field to drag anywhere.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1"/>
+    <row r="12" ht="18" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="A8:E8"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -477,296 +571,311 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>The same data in two shapes</t>
+          <t>Wide — one row per RM</t>
         </is>
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Both tables below hold exactly the same numbers.  In the WIDE table the crop is the column heading.  In the LONG table the crop is a value in its own column, and every yield is stacked into one column.  A PivotTable can only group by something that lives in its own column.</t>
+          <t>Three crops, three columns.  The crop name is a column heading, so it is part of the layout rather than part of the data.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1"/>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>WIDE — one row per RM</t>
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>RM</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Wheat</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Canola</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Barley</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>55.7</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1"/>
+    <row r="9" ht="18" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Long — one row per RM and crop</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="44" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>The same nine numbers.  Crop is now a column of values and every yield sits in a single Yield column, which is the shape a PivotTable needs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1"/>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>RM</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Crop</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Yield</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="10" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Wheat</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="9" t="n">
+        <v>50.8</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="10" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Canola</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="D6" s="9" t="n">
+        <v>36.8</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="10" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>Barley</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="6" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="E6" s="7" t="n">
+      <c r="D7" s="9" t="n">
         <v>53</v>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="6" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B7" s="6" t="n">
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="10" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B8" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Wheat</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
         <v>48.5</v>
       </c>
-      <c r="D7" s="7" t="n">
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="10" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Canola</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
         <v>34.4</v>
       </c>
-      <c r="E7" s="7" t="n">
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="10" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Barley</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n">
         <v>50.5</v>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B8" s="6" t="n">
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="10" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B11" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Wheat</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
         <v>52.1</v>
       </c>
-      <c r="D8" s="7" t="n">
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="10" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B12" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Canola</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
         <v>38.9</v>
       </c>
-      <c r="E8" s="7" t="n">
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="10" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Barley</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n">
         <v>55.7</v>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1"/>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>LONG — one row per RM and crop</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>RM</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Crop</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Yield</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B12" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Wheat</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>50.8</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B13" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Canola</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>36.8</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Barley</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B15" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Wheat</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>48.5</v>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B16" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Canola</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>34.4</v>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B17" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Barley</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>50.5</v>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B18" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Wheat</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="n">
-        <v>52.1</v>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B19" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Canola</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>38.9</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B20" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Barley</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>55.7</v>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1"/>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>Ask for the average yield of each crop.  In the long table that is one PivotTable — Crop on Rows, Yield in Values.  In the wide table you cannot do it in one move, because there is no single Crop field to drag anywhere.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1"/>
+    <row r="14" ht="18" customHeight="1"/>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A22:F22"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/textbook_examples/mod01_wide_long.xlsx
+++ b/textbook_examples/mod01_wide_long.xlsx
@@ -493,7 +493,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>The next two tabs hold exactly the same numbers — three rural municipalities, three crops, one year — laid out two different ways.  Open them side by side and compare.</t>
+          <t>The next two tabs — Wide and Long — hold exactly the same numbers: three rural municipalities, three crops, one year, laid out two different ways.  Use the tabs along the bottom of the window to switch between them.</t>
         </is>
       </c>
     </row>
@@ -550,8 +550,8 @@
     <mergeCell ref="A8:E8"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId2"/>
+    <hyperlink ref="A4" location="'Wide'!A1"/>
+    <hyperlink ref="A6" location="'Long'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
